--- a/exam_forms/007_microbial_virulence_factors_quiz--exam_forms.xlsx
+++ b/exam_forms/007_microbial_virulence_factors_quiz--exam_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,11 +437,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -515,40 +515,40 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>introduction</t>
+          <t>question_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Introduction</t>
+          <t>What are the primary virulence factors of E. coli?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>question_1</t>
+          <t>question_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>What are the primary virulence factors of E. coli?</t>
+          <t>Which of the following bacteria are known for their high virulence?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>question_2</t>
+          <t>question_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Which of the following bacteria are known for their high virulence?</t>
+          <t>How does the virulence of E. coli differ from other bacteria?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>question_3</t>
+          <t>question_4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>How does the virulence of E. coli differ from other bacteria?</t>
+          <t>What is the primary virulence factor of Staphylococcus aureus?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>question_4</t>
+          <t>question_5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>What is the primary virulence factor of Staphylococcus aureus?</t>
+          <t>Which of the following are virulence factors for S. aureus?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>question_5</t>
+          <t>question_6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Which of the following are virulence factors for S. aureus?</t>
+          <t>What is the primary virulence factor of S. aureus?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>question_6</t>
+          <t>question_7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>What is the primary virulence factor of S. aureus?</t>
+          <t>Which of the following are virulence factors for Listeria?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,40 +676,40 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>question_7</t>
+          <t>question_8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>What is the virulence factor of Listeria?</t>
+          <t>Question 8</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>question_8</t>
+          <t>question_9</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Which of the following bacteria are known for their high virulence?</t>
+          <t>Question 9</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,40 +722,40 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>question_9</t>
+          <t>question_10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>How does the virulence of E. coli differ from other bacteria?</t>
+          <t>What is the primary virulence factor of E. coli?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>question_10</t>
+          <t>question_11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>What is the primary virulence factor of E. coli?</t>
+          <t>Which of the following are virulence factors for E. coli?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,320 +768,21 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>question_11</t>
+          <t>question_12</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Which of the following are virulence factors for E. coli?</t>
+          <t>What is the primary virulence factor of S. cerevisiae?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>question_12</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>What is the virulence factor of S. cerevisiae?</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>question_13</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>How does the virulence of S. aureus differ from other bacteria?</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>question_14</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Which of the following are not virulence factors for S. aureus?</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>question_16</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Which of the following are virulence factors for E. coli?</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>question_17</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>What is the primary virulence factor of S. aureus?</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>question_18</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>What are the virulence factors of S. aureus?</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>question_19</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>What is the primary virulence factor of E. coli?</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>question_20</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>How does the virulence of S. aureus differ from other bacteria?</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>question_21</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Which of the following are not virulence factors for S. aureus?</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>question_22</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>What is the primary virulence factor of E. coli?</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>question_23</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Which of the following are virulence factors for S. aureus?</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>question_24</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>What is the primary virulence factor of S. aureus?</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>question_25</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>What are the virulence factors of E. coli?</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -1098,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C61"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +832,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>virulence_factors</t>
+          <t>adhesive_molecules</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Virulence Factors</t>
+          <t>Adhesive molecules</t>
         </is>
       </c>
     </row>
@@ -1148,12 +849,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>another_factor</t>
+          <t>invasion_factors</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Another Factor</t>
+          <t>Invasion factors</t>
         </is>
       </c>
     </row>
@@ -1165,12 +866,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>even_more</t>
+          <t>toxin_production</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Even More</t>
+          <t>Toxin production</t>
         </is>
       </c>
     </row>
@@ -1182,12 +883,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>bacterium_a</t>
+          <t>e._coli</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bacterium A</t>
+          <t>E. coli</t>
         </is>
       </c>
     </row>
@@ -1199,12 +900,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>bacterium_b</t>
+          <t>s._aureus</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bacterium B</t>
+          <t>S. aureus</t>
         </is>
       </c>
     </row>
@@ -1216,121 +917,121 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>bacterium_c</t>
+          <t>listeria</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bacterium C</t>
+          <t>Listeria</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>question_4_choices</t>
+          <t>question_3_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>factor_a</t>
+          <t>virulence_factor_type</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Factor A</t>
+          <t>Virulence factor type</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>question_4_choices</t>
+          <t>question_3_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>factor_b</t>
+          <t>virulence_factor_amount</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Factor B</t>
+          <t>Virulence factor amount</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>question_4_choices</t>
+          <t>question_3_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>factor_c</t>
+          <t>virulence_factor_strength</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Factor C</t>
+          <t>Virulence factor strength</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>question_5_choices</t>
+          <t>question_4_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>factor_1</t>
+          <t>factor_a</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Factor 1</t>
+          <t>Factor A</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>question_5_choices</t>
+          <t>question_4_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>factor_2</t>
+          <t>factor_b</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Factor 2</t>
+          <t>Factor B</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>question_5_choices</t>
+          <t>question_4_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>factor_3</t>
+          <t>factor_c</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Factor 3</t>
+          <t>Factor C</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>question_6_choices</t>
+          <t>question_5_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1347,7 +1048,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>question_6_choices</t>
+          <t>question_5_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1364,7 +1065,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>question_6_choices</t>
+          <t>question_5_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1381,211 +1082,211 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>question_7_choices</t>
+          <t>question_6_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>factor_1</t>
+          <t>factor_a</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Factor 1</t>
+          <t>Factor A</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>question_7_choices</t>
+          <t>question_6_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>factor_2</t>
+          <t>factor_b</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Factor 2</t>
+          <t>Factor B</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>question_7_choices</t>
+          <t>question_6_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>factor_3</t>
+          <t>factor_c</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Factor 3</t>
+          <t>Factor C</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>question_8_choices</t>
+          <t>question_7_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>bacterium_d</t>
+          <t>factor_1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bacterium D</t>
+          <t>Factor 1</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>question_8_choices</t>
+          <t>question_7_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>bacterium_e</t>
+          <t>factor_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bacterium E</t>
+          <t>Factor 2</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>question_8_choices</t>
+          <t>question_7_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>bacterium_f</t>
+          <t>factor_3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bacterium F</t>
+          <t>Factor 3</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>question_10_choices</t>
+          <t>question_8_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>factor_a</t>
+          <t>bacterium_d</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Factor A</t>
+          <t>Bacterium D</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>question_10_choices</t>
+          <t>question_8_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>factor_b</t>
+          <t>bacterium_e</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Factor B</t>
+          <t>Bacterium E</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>question_10_choices</t>
+          <t>question_8_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>factor_c</t>
+          <t>bacterium_f</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Factor C</t>
+          <t>Bacterium F</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>question_11_choices</t>
+          <t>question_9_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>factor_1</t>
+          <t>virulence_factor_type</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Factor 1</t>
+          <t>Virulence factor type</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>question_11_choices</t>
+          <t>question_9_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>factor_2</t>
+          <t>virulence_factor_amount</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Factor 2</t>
+          <t>Virulence factor amount</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>question_11_choices</t>
+          <t>question_9_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>factor_3</t>
+          <t>virulence_factor_strength</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Factor 3</t>
+          <t>Virulence factor strength</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>question_12_choices</t>
+          <t>question_10_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1602,7 +1303,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>question_12_choices</t>
+          <t>question_10_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1619,7 +1320,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>question_12_choices</t>
+          <t>question_10_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1636,510 +1337,102 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>question_14_choices</t>
+          <t>question_11_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>not_a</t>
+          <t>factor_1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Not A</t>
+          <t>Factor 1</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>question_14_choices</t>
+          <t>question_11_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>not_b</t>
+          <t>factor_2</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Not B</t>
+          <t>Factor 2</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>question_14_choices</t>
+          <t>question_11_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>not_c</t>
+          <t>factor_3</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Not C</t>
+          <t>Factor 3</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>question_16_choices</t>
+          <t>question_12_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>factor_1</t>
+          <t>factor_a</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Factor 1</t>
+          <t>Factor A</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>question_16_choices</t>
+          <t>question_12_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>factor_2</t>
+          <t>factor_b</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Factor 2</t>
+          <t>Factor B</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>question_16_choices</t>
+          <t>question_12_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>factor_3</t>
+          <t>factor_c</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Factor 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>question_17_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>factor_a</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Factor A</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>question_17_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>factor_b</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Factor B</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>question_17_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>factor_c</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
           <t>Factor C</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>question_18_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>factor_1</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Factor 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>question_18_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>factor_2</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Factor 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>question_18_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>factor_3</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Factor 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>question_19_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>factor_a</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Factor A</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>question_19_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>factor_b</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Factor B</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>question_19_choices</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>factor_c</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Factor C</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>question_21_choices</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>not_a</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Not A</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>question_21_choices</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>not_b</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Not B</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>question_21_choices</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>not_c</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Not C</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>question_22_choices</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>factor_a</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Factor A</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>question_22_choices</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>factor_b</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Factor B</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>question_22_choices</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>factor_c</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Factor C</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>question_23_choices</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>factor_1</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Factor 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>question_23_choices</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>factor_2</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Factor 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>question_23_choices</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>factor_3</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Factor 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>question_24_choices</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>factor_a</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Factor A</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>question_24_choices</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>factor_b</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Factor B</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>question_24_choices</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>factor_c</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Factor C</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>question_25_choices</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>factor_1</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Factor 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>question_25_choices</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>factor_2</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Factor 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>question_25_choices</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>factor_3</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Factor 3</t>
         </is>
       </c>
     </row>
